--- a/data/trending_integrated_20261012_13.xlsx
+++ b/data/trending_integrated_20261012_13.xlsx
@@ -581,10 +581,10 @@
         <v>57</v>
       </c>
       <c r="F2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19912717620</v>
+        <v>19934478060</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -670,13 +670,13 @@
         <v>0.91</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
         <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>131837024810</v>
+        <v>131867334470</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -711,7 +711,7 @@
         <v>465</v>
       </c>
       <c r="R3" t="n">
-        <v>15000</v>
+        <v>129000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13590</v>
+        <v>13700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+21.99%</t>
+          <t>'+22.98%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F4" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G4" t="n">
         <v>313</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>158079232255</v>
+        <v>161489628395</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -803,14 +803,14 @@
         <v>3200</v>
       </c>
       <c r="R4" t="n">
-        <v>-487000</v>
+        <v>-446000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외국인 매도세 관찰, 금호전기 상장 및 흐름 연계 가능성 언급.</t>
+          <t>금호건설, 호남 지역 건설사로서의 특성 언급. 금호전기 상장과 연동 가능성 및 외국인 대량 매도 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['외국인', '매도', '상장']</t>
+          <t>['호남', '외국인 매도', '금호전기']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1606</v>
+        <v>1600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.79%</t>
+          <t>'+15.36%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
         <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>10708857587</v>
+        <v>10759841179</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>녹십자엠에스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15200</v>
+        <v>3980</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.27%</t>
+          <t>'+6.56%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.12</v>
+        <v>-1.19</v>
       </c>
       <c r="E6" t="n">
-        <v>202</v>
+        <v>83</v>
       </c>
       <c r="F6" t="n">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>326</v>
+        <v>93</v>
       </c>
       <c r="H6" t="n">
-        <v>0.21</v>
+        <v>0.78</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13910</v>
+        <v>3735</v>
       </c>
       <c r="K6" t="n">
-        <v>13350</v>
+        <v>3660</v>
       </c>
       <c r="L6" t="n">
-        <v>15790</v>
+        <v>4300</v>
       </c>
       <c r="M6" t="n">
-        <v>13350</v>
+        <v>3660</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09</v>
+        <v>1.97</v>
       </c>
       <c r="O6" t="n">
-        <v>134825830010</v>
+        <v>65444708988</v>
       </c>
       <c r="P6" t="n">
-        <v>28700</v>
+        <v>6660</v>
       </c>
       <c r="Q6" t="n">
-        <v>11600</v>
+        <v>2200</v>
       </c>
       <c r="R6" t="n">
-        <v>-3000</v>
+        <v>-4000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>방산 및 우주 테마 연계, 누리호 발사 성공 관련 긍정적 언급 및 상장 가능성 기대.</t>
+          <t>중국 방역 강화 선포와 관련된 러시아 발 이슈 언급. 2만원 목표가 및 매도 후 수익 챙김.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['방산', '우주', '누리호']</t>
+          <t>['러시아', '중국 방역', '수익']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>142280</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>녹십자엠에스</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3985</v>
+        <v>14730</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.69%</t>
+          <t>'+5.90%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.19</v>
+        <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="F7" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="G7" t="n">
-        <v>90</v>
+        <v>340</v>
       </c>
       <c r="H7" t="n">
-        <v>0.78</v>
+        <v>0.21</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3735</v>
+        <v>13910</v>
       </c>
       <c r="K7" t="n">
-        <v>3660</v>
+        <v>13350</v>
       </c>
       <c r="L7" t="n">
-        <v>4300</v>
+        <v>15790</v>
       </c>
       <c r="M7" t="n">
-        <v>3660</v>
+        <v>13350</v>
       </c>
       <c r="N7" t="n">
-        <v>1.97</v>
+        <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>64077684304</v>
+        <v>140399021445</v>
       </c>
       <c r="P7" t="n">
-        <v>6660</v>
+        <v>28700</v>
       </c>
       <c r="Q7" t="n">
-        <v>2200</v>
+        <v>11600</v>
       </c>
       <c r="R7" t="n">
-        <v>-4000</v>
+        <v>-3000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>러시아 발 방역 강화 관련 언급, 주가 상승 및 하락 가능성 혼재.</t>
+          <t>방산·우주 테마 연관성 및 미국 팔란티어 상승세 언급. 보호예수 해제 및 투자 심리 분석.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['러시아', '방역', '주가']</t>
+          <t>['방산', '우주 테마', '보호예수']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>142280</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
@@ -1130,13 +1130,13 @@
         <v>-1.1</v>
       </c>
       <c r="E8" t="n">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F8" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="H8" t="n">
         <v>1.99</v>
@@ -1162,7 +1162,7 @@
         <v>3.09</v>
       </c>
       <c r="O8" t="n">
-        <v>100899625465</v>
+        <v>103498355160</v>
       </c>
       <c r="P8" t="n">
         <v>23500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>성수 메가프로젝트 관련 건설 기초 소재 사업 기대감. 반도체 수요 겨냥 투자 소식.</t>
+          <t>성수메가프로젝트 및 건설기초소재 대장주로서의 역할 언급. 공매도 쇼퀴즈 기대 및 국토부 승인 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['건설', '투자', '반도체']</t>
+          <t>['건설기초소재', '공매도', '성수메가프로젝트']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="F9" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G9" t="n">
-        <v>2616</v>
+        <v>2638</v>
       </c>
       <c r="H9" t="n">
         <v>13.33</v>
@@ -1254,7 +1254,7 @@
         <v>13.39</v>
       </c>
       <c r="O9" t="n">
-        <v>34092848650</v>
+        <v>34222509100</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10990</v>
+        <v>11080</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.09%</t>
+          <t>'-2.29%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.03</v>
       </c>
       <c r="E10" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H10" t="n">
         <v>0.41</v>
@@ -1346,7 +1346,7 @@
         <v>0.44</v>
       </c>
       <c r="O10" t="n">
-        <v>28998320695</v>
+        <v>29212165625</v>
       </c>
       <c r="P10" t="n">
         <v>29750</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16120</v>
+        <v>16140</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.30%</t>
+          <t>'-3.18%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F11" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>659</v>
+        <v>675</v>
       </c>
       <c r="H11" t="n">
         <v>9.470000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.460000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>47922030400</v>
+        <v>48484797950</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1447,10 +1447,10 @@
         <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>367000</v>
+        <v>540000</v>
       </c>
       <c r="S11" t="n">
-        <v>17000</v>
+        <v>-97000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2225</v>
+        <v>2230</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.47%</t>
+          <t>'-3.25%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H12" t="n">
         <v>1.48</v>
@@ -1530,7 +1530,7 @@
         <v>1.32</v>
       </c>
       <c r="O12" t="n">
-        <v>30021050068</v>
+        <v>30142421902</v>
       </c>
       <c r="P12" t="n">
         <v>2465</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18180</v>
+        <v>253250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.61%</t>
+          <t>'-3.34%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>113</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>65</v>
+        <v>474</v>
       </c>
       <c r="G13" t="n">
-        <v>326</v>
+        <v>1790</v>
       </c>
       <c r="H13" t="n">
-        <v>27.61</v>
+        <v>46.35</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18860</v>
+        <v>262000</v>
       </c>
       <c r="K13" t="n">
-        <v>18690</v>
+        <v>260000</v>
       </c>
       <c r="L13" t="n">
-        <v>18760</v>
+        <v>262500</v>
       </c>
       <c r="M13" t="n">
-        <v>18100</v>
+        <v>252000</v>
       </c>
       <c r="N13" t="n">
-        <v>27.68</v>
+        <v>46.38</v>
       </c>
       <c r="O13" t="n">
-        <v>35362027655</v>
+        <v>2499083455250</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>18100</v>
+        <v>90200</v>
       </c>
       <c r="R13" t="n">
-        <v>29000</v>
+        <v>-1423000</v>
       </c>
       <c r="S13" t="n">
-        <v>23000</v>
+        <v>-345000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈와 주가 연계, 수주 랠리에도 불구하고 하락세 언급 및 부정적 전망.</t>
+          <t>정치적 이슈와 연관된 주가 하락 분석. 정부 정책 및 특정 정치인에 대한 비판.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수주', '정치', '하락']</t>
+          <t>['정치', '하락', '정부 정책']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>252000</v>
+        <v>18170</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.82%</t>
+          <t>'-3.66%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>113</v>
       </c>
       <c r="F14" t="n">
-        <v>478</v>
+        <v>64</v>
       </c>
       <c r="G14" t="n">
-        <v>1737</v>
+        <v>321</v>
       </c>
       <c r="H14" t="n">
-        <v>46.35</v>
+        <v>27.61</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>262000</v>
+        <v>18860</v>
       </c>
       <c r="K14" t="n">
-        <v>260000</v>
+        <v>18690</v>
       </c>
       <c r="L14" t="n">
-        <v>262500</v>
+        <v>18760</v>
       </c>
       <c r="M14" t="n">
-        <v>252000</v>
+        <v>18100</v>
       </c>
       <c r="N14" t="n">
-        <v>46.38</v>
+        <v>27.68</v>
       </c>
       <c r="O14" t="n">
-        <v>2433598055750</v>
+        <v>36210556155</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>90200</v>
+        <v>18100</v>
       </c>
       <c r="R14" t="n">
-        <v>-416000</v>
+        <v>112000</v>
       </c>
       <c r="S14" t="n">
-        <v>-81000</v>
+        <v>33000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 주가 하락 언급, 부정적 전망 및 실적 발표 영향 우려.</t>
+          <t>조선주 순환매 및 LNG·FLNG 수주 랠리 언급. 현대로템, 한화오션과의 비교 및 국내 증시 하락세 분석.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['정치', '하락', '실적']</t>
+          <t>['조선주', '수주', 'LNG']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1615000</v>
+        <v>1616000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.93%</t>
+          <t>'-3.87%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="G15" t="n">
-        <v>1964</v>
+        <v>1987</v>
       </c>
       <c r="H15" t="n">
         <v>49.52</v>
@@ -1806,7 +1806,7 @@
         <v>49.59</v>
       </c>
       <c r="O15" t="n">
-        <v>2840342006000</v>
+        <v>2918596788000</v>
       </c>
       <c r="P15" t="n">
         <v>2987000</v>
@@ -1815,14 +1815,14 @@
         <v>403000</v>
       </c>
       <c r="R15" t="n">
-        <v>-276000</v>
+        <v>-246000</v>
       </c>
       <c r="S15" t="n">
-        <v>14000</v>
+        <v>13000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 주가 하락 언급, 자회사 상장 관련 부정적 의견.</t>
+          <t>정치적 이슈와 연계된 SK하이닉스 주가 하락 분석. 자사주 매입 및 호남 반도체 관련 논란 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['정치', '하락', '자회사']</t>
+          <t>['정치', '하락', '자사주']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7710</v>
+        <v>7720</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.51%</t>
+          <t>'-5.39%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F16" t="n">
         <v>89</v>
       </c>
       <c r="G16" t="n">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="H16" t="n">
         <v>26.37</v>
@@ -1898,7 +1898,7 @@
         <v>26.38</v>
       </c>
       <c r="O16" t="n">
-        <v>22277085150</v>
+        <v>22917366135</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1907,14 +1907,14 @@
         <v>7700</v>
       </c>
       <c r="R16" t="n">
-        <v>-595000</v>
+        <v>-1097000</v>
       </c>
       <c r="S16" t="n">
-        <v>2000</v>
+        <v>-30000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>투자 심리 악화 및 유상증자 가능성 제기, 주가 하락 및 회복 불능 전망.</t>
+          <t>LG디스플레이의 낮은 목표가 및 회복 불능 차트 분석. 유상증자 가능성과 회사의 장기적 전망에 대한 부정적 평가.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['투자심리', '유상증자', '하락']</t>
+          <t>['목표가', '차트', '유상증자']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15890</v>
+        <v>15850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.36%</t>
+          <t>'-6.60%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.6</v>
       </c>
       <c r="E17" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F17" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G17" t="n">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="H17" t="n">
         <v>3.37</v>
@@ -1990,7 +1990,7 @@
         <v>3.97</v>
       </c>
       <c r="O17" t="n">
-        <v>72356650880</v>
+        <v>73040660030</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>AI 및 광통신 테마 성장 기대감. 3분기 어닝 서프라이즈 기록.</t>
+          <t>3분기 어닝 서프라이즈 및 광통신 시장 성장률 분석. 유튜버 활동과 공매도 규제 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '실적']</t>
+          <t>['어닝 서프라이즈', '광통신', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25950</v>
+        <v>3940</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.65%</t>
+          <t>'-7.73%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-2.94</v>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F18" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="G18" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="H18" t="n">
-        <v>9.460000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>28100</v>
+        <v>4270</v>
       </c>
       <c r="K18" t="n">
-        <v>27600</v>
+        <v>4150</v>
       </c>
       <c r="L18" t="n">
-        <v>27800</v>
+        <v>4495</v>
       </c>
       <c r="M18" t="n">
-        <v>25850</v>
+        <v>3905</v>
       </c>
       <c r="N18" t="n">
-        <v>10.02</v>
+        <v>4.46</v>
       </c>
       <c r="O18" t="n">
-        <v>50472738825</v>
+        <v>17872486082</v>
       </c>
       <c r="P18" t="n">
-        <v>75900</v>
+        <v>5470</v>
       </c>
       <c r="Q18" t="n">
-        <v>15960</v>
+        <v>2810</v>
       </c>
       <c r="R18" t="n">
-        <v>-9000</v>
+        <v>-89000</v>
       </c>
       <c r="S18" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>경영진의 무능력 지적, LS 기술유출 타격 언급. 실적 개선 근거 부족 및 투매 우려.</t>
+          <t>러시아 코로나 관련 뉴스 언급, 모더나 급등 영향 분석. 명확한 모멘텀 부재 속 단기적 기대감.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['경영진 부진', '기술유출', '실적 우려']</t>
+          <t>['코로나19', '모더나', '단기 모멘텀']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3940</v>
+        <v>25925</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.73%</t>
+          <t>'-7.74%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-2.94</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>1.52</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>4270</v>
+        <v>28100</v>
       </c>
       <c r="K19" t="n">
-        <v>4150</v>
+        <v>27600</v>
       </c>
       <c r="L19" t="n">
-        <v>4495</v>
+        <v>27800</v>
       </c>
       <c r="M19" t="n">
-        <v>3915</v>
+        <v>25850</v>
       </c>
       <c r="N19" t="n">
-        <v>4.46</v>
+        <v>10.02</v>
       </c>
       <c r="O19" t="n">
-        <v>17738993347</v>
+        <v>51480240250</v>
       </c>
       <c r="P19" t="n">
-        <v>5470</v>
+        <v>75900</v>
       </c>
       <c r="Q19" t="n">
-        <v>2810</v>
+        <v>15960</v>
       </c>
       <c r="R19" t="n">
-        <v>-92000</v>
+        <v>-64000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>러시아 코로나 관련 뉴스 언급, 모더나 급등 영향 분석. 명확한 모멘텀 부재 속 단기적 기대감.</t>
+          <t>경영진의 무능력 지적, LS 기술유출 타격 언급. 실적 개선 근거 부족 및 투매 우려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['코로나19', '모더나', '단기 모멘텀']</t>
+          <t>['경영진 부진', '기술유출', '실적 우려']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>001440</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261012_13.xlsx
+++ b/data/trending_integrated_20261012_13.xlsx
@@ -578,13 +578,13 @@
         <v>0.61</v>
       </c>
       <c r="E2" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19934478060</v>
+        <v>19936708860</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -670,13 +670,13 @@
         <v>0.91</v>
       </c>
       <c r="E3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>131867334470</v>
+        <v>131916950210</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13700</v>
+        <v>13900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+22.98%</t>
+          <t>'+24.78%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G4" t="n">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>161489628395</v>
+        <v>166606941630</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -843,18 +843,18 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1600</v>
+        <v>1633</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.36%</t>
+          <t>'+17.74%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F5" t="n">
         <v>31</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>10759841179</v>
+        <v>11028037015</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -895,7 +895,7 @@
         <v>910</v>
       </c>
       <c r="R5" t="n">
-        <v>-270000</v>
+        <v>-392000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3980</v>
+        <v>4010</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.56%</t>
+          <t>'+7.36%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.19</v>
       </c>
       <c r="E6" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H6" t="n">
         <v>0.78</v>
@@ -978,7 +978,7 @@
         <v>1.97</v>
       </c>
       <c r="O6" t="n">
-        <v>65444708988</v>
+        <v>66026971074</v>
       </c>
       <c r="P6" t="n">
         <v>6660</v>
@@ -987,23 +987,23 @@
         <v>2200</v>
       </c>
       <c r="R6" t="n">
-        <v>-4000</v>
+        <v>60000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-79000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>중국 방역 강화 선포와 관련된 러시아 발 이슈 언급. 2만원 목표가 및 매도 후 수익 챙김.</t>
+          <t>중국 방역 강화 및 러시아 관련 이슈에 따른 상승 가능성 및 매도 신호 혼재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['러시아', '중국 방역', '수익']</t>
+          <t>['러시아', '방역', '수익']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14730</v>
+        <v>14780</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.90%</t>
+          <t>'+6.25%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="F7" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="H7" t="n">
         <v>0.21</v>
@@ -1070,7 +1070,7 @@
         <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>140399021445</v>
+        <v>142192376425</v>
       </c>
       <c r="P7" t="n">
         <v>28700</v>
@@ -1079,23 +1079,23 @@
         <v>11600</v>
       </c>
       <c r="R7" t="n">
-        <v>-3000</v>
+        <v>-15000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>방산·우주 테마 연관성 및 미국 팔란티어 상승세 언급. 보호예수 해제 및 투자 심리 분석.</t>
+          <t>방산 및 우주 테마와 연계된 주가 상승 기대감 속 보호예수 해제 변동성 우려.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['방산', '우주 테마', '보호예수']</t>
+          <t>['방산', '우주', '보호예수']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7350</v>
+        <v>7480</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.81%</t>
+          <t>'+5.65%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-1.1</v>
       </c>
       <c r="E8" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G8" t="n">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="H8" t="n">
         <v>1.99</v>
@@ -1162,7 +1162,7 @@
         <v>3.09</v>
       </c>
       <c r="O8" t="n">
-        <v>103498355160</v>
+        <v>106015019665</v>
       </c>
       <c r="P8" t="n">
         <v>23500</v>
@@ -1171,10 +1171,10 @@
         <v>2890</v>
       </c>
       <c r="R8" t="n">
-        <v>-136000</v>
+        <v>-79000</v>
       </c>
       <c r="S8" t="n">
-        <v>9000</v>
+        <v>246000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44850</v>
+        <v>11150</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.75%</t>
+          <t>'-1.68%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="E9" t="n">
-        <v>416</v>
+        <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>239</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>2638</v>
+        <v>93</v>
       </c>
       <c r="H9" t="n">
-        <v>13.33</v>
+        <v>0.41</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>45650</v>
+        <v>11340</v>
       </c>
       <c r="K9" t="n">
-        <v>47550</v>
+        <v>11340</v>
       </c>
       <c r="L9" t="n">
-        <v>47550</v>
+        <v>12470</v>
       </c>
       <c r="M9" t="n">
-        <v>43900</v>
+        <v>10810</v>
       </c>
       <c r="N9" t="n">
-        <v>13.39</v>
+        <v>0.44</v>
       </c>
       <c r="O9" t="n">
-        <v>34222509100</v>
+        <v>29322630165</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>29750</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>10810</v>
       </c>
       <c r="R9" t="n">
-        <v>-115000</v>
+        <v>8000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>FDA 간암 1차 치료제 리보세라닙 재승인 서류 제출 공시 확인. 연말 30만 기대감.</t>
+          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA', '리보세라닙', '재신청']</t>
+          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11080</v>
+        <v>44800</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.29%</t>
+          <t>'-1.86%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>57</v>
+        <v>424</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>244</v>
       </c>
       <c r="G10" t="n">
-        <v>89</v>
+        <v>2679</v>
       </c>
       <c r="H10" t="n">
-        <v>0.41</v>
+        <v>13.33</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,222 +1331,222 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>11340</v>
+        <v>45650</v>
       </c>
       <c r="K10" t="n">
-        <v>11340</v>
+        <v>47550</v>
       </c>
       <c r="L10" t="n">
-        <v>12470</v>
+        <v>47550</v>
       </c>
       <c r="M10" t="n">
-        <v>10810</v>
+        <v>43900</v>
       </c>
       <c r="N10" t="n">
-        <v>0.44</v>
+        <v>13.39</v>
       </c>
       <c r="O10" t="n">
-        <v>29212165625</v>
+        <v>34596604175</v>
       </c>
       <c r="P10" t="n">
-        <v>29750</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>10810</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>46000</v>
+        <v>-112000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
+          <t>FDA 간암 1차 치료제 리보세라닙 재승인 서류 제출 공시 확인. 연말 30만 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
+          <t>['FDA', '리보세라닙', '재신청']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>486510</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16140</v>
+        <v>2235</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.18%</t>
+          <t>'-3.04%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="E11" t="n">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="F11" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>675</v>
+        <v>130</v>
       </c>
       <c r="H11" t="n">
-        <v>9.470000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16670</v>
+        <v>2305</v>
       </c>
       <c r="K11" t="n">
-        <v>16500</v>
+        <v>2430</v>
       </c>
       <c r="L11" t="n">
-        <v>16870</v>
+        <v>2445</v>
       </c>
       <c r="M11" t="n">
-        <v>16050</v>
+        <v>2210</v>
       </c>
       <c r="N11" t="n">
-        <v>9.460000000000001</v>
+        <v>1.32</v>
       </c>
       <c r="O11" t="n">
-        <v>48484797950</v>
+        <v>30223115632</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>2465</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>865</v>
       </c>
       <c r="R11" t="n">
-        <v>540000</v>
+        <v>-498000</v>
       </c>
       <c r="S11" t="n">
-        <v>-97000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대차거래 해지 및 뱅크런 관련 의혹 제기, 주가 하락 관련 부정적 언급.</t>
+          <t>인공지능 데이터센터 확대 따른 에너지저장장치용 유연회로기판 매출 급증 기대. 단기 급등 후 차익실현 압력.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['대차', '뱅크런', '주가']</t>
+          <t>['AI 데이터센터', 'ESS', '유연회로기판']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2230</v>
+        <v>16140</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.25%</t>
+          <t>'-3.18%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.16</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="G12" t="n">
-        <v>130</v>
+        <v>689</v>
       </c>
       <c r="H12" t="n">
-        <v>1.48</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2305</v>
+        <v>16670</v>
       </c>
       <c r="K12" t="n">
-        <v>2430</v>
+        <v>16500</v>
       </c>
       <c r="L12" t="n">
-        <v>2445</v>
+        <v>16870</v>
       </c>
       <c r="M12" t="n">
-        <v>2210</v>
+        <v>16050</v>
       </c>
       <c r="N12" t="n">
-        <v>1.32</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>30142421902</v>
+        <v>48951966830</v>
       </c>
       <c r="P12" t="n">
-        <v>2465</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>865</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-442000</v>
+        <v>544000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-97000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 확대 따른 에너지저장장치용 유연회로기판 매출 급증 기대. 단기 급등 후 차익실현 압력.</t>
+          <t>대규모 대차 거래 해지 및 뱅크런 가능성 제기로 인한 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,20 +1555,20 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', 'ESS', '유연회로기판']</t>
+          <t>['대차거래', '뱅크런', '주주연대']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253250</v>
+        <v>252750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.34%</t>
+          <t>'-3.53%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="G13" t="n">
-        <v>1790</v>
+        <v>1853</v>
       </c>
       <c r="H13" t="n">
         <v>46.35</v>
@@ -1622,7 +1622,7 @@
         <v>46.38</v>
       </c>
       <c r="O13" t="n">
-        <v>2499083455250</v>
+        <v>2582027273750</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1631,23 +1631,23 @@
         <v>90200</v>
       </c>
       <c r="R13" t="n">
-        <v>-1423000</v>
+        <v>-1433000</v>
       </c>
       <c r="S13" t="n">
         <v>-345000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관된 주가 하락 분석. 정부 정책 및 특정 정치인에 대한 비판.</t>
+          <t>정치적 이슈로 인한 급락 및 외인/기관 매도 우려 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치', '하락', '정부 정책']</t>
+          <t>['정치', '반도체', '외인']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18170</v>
+        <v>1619000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.66%</t>
+          <t>'-3.69%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>113</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>64</v>
+        <v>519</v>
       </c>
       <c r="G14" t="n">
-        <v>321</v>
+        <v>1967</v>
       </c>
       <c r="H14" t="n">
-        <v>27.61</v>
+        <v>49.52</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18860</v>
+        <v>1681000</v>
       </c>
       <c r="K14" t="n">
-        <v>18690</v>
+        <v>1640000</v>
       </c>
       <c r="L14" t="n">
-        <v>18760</v>
+        <v>1653000</v>
       </c>
       <c r="M14" t="n">
-        <v>18100</v>
+        <v>1605000</v>
       </c>
       <c r="N14" t="n">
-        <v>27.68</v>
+        <v>49.59</v>
       </c>
       <c r="O14" t="n">
-        <v>36210556155</v>
+        <v>2984378343000</v>
       </c>
       <c r="P14" t="n">
-        <v>35350</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>18100</v>
+        <v>403000</v>
       </c>
       <c r="R14" t="n">
-        <v>112000</v>
+        <v>-244000</v>
       </c>
       <c r="S14" t="n">
-        <v>33000</v>
+        <v>13000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>조선주 순환매 및 LNG·FLNG 수주 랠리 언급. 현대로템, 한화오션과의 비교 및 국내 증시 하락세 분석.</t>
+          <t>정치적 요인으로 인한 증시 하락 및 반도체 업황 부진에 따른 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['조선주', '수주', 'LNG']</t>
+          <t>['SK하이닉스', '반도체', '정치']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1616000</v>
+        <v>18160</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.87%</t>
+          <t>'-3.71%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>114</v>
       </c>
       <c r="F15" t="n">
-        <v>518</v>
+        <v>64</v>
       </c>
       <c r="G15" t="n">
-        <v>1987</v>
+        <v>321</v>
       </c>
       <c r="H15" t="n">
-        <v>49.52</v>
+        <v>27.61</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1681000</v>
+        <v>18860</v>
       </c>
       <c r="K15" t="n">
-        <v>1640000</v>
+        <v>18690</v>
       </c>
       <c r="L15" t="n">
-        <v>1653000</v>
+        <v>18760</v>
       </c>
       <c r="M15" t="n">
-        <v>1605000</v>
+        <v>18100</v>
       </c>
       <c r="N15" t="n">
-        <v>49.59</v>
+        <v>27.68</v>
       </c>
       <c r="O15" t="n">
-        <v>2918596788000</v>
+        <v>36826209765</v>
       </c>
       <c r="P15" t="n">
-        <v>2987000</v>
+        <v>35350</v>
       </c>
       <c r="Q15" t="n">
-        <v>403000</v>
+        <v>18100</v>
       </c>
       <c r="R15" t="n">
-        <v>-246000</v>
+        <v>112000</v>
       </c>
       <c r="S15" t="n">
-        <v>13000</v>
+        <v>33000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 SK하이닉스 주가 하락 분석. 자사주 매입 및 호남 반도체 관련 논란 언급.</t>
+          <t>조선주 순환매 및 LNG·FLNG 수주 랠리 언급. 현대로템, 한화오션과의 비교 및 국내 증시 하락세 분석.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['정치', '하락', '자사주']</t>
+          <t>['조선주', '수주', 'LNG']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7720</v>
+        <v>7750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.39%</t>
+          <t>'-5.02%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F16" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G16" t="n">
-        <v>727</v>
+        <v>737</v>
       </c>
       <c r="H16" t="n">
         <v>26.37</v>
@@ -1898,7 +1898,7 @@
         <v>26.38</v>
       </c>
       <c r="O16" t="n">
-        <v>22917366135</v>
+        <v>23386454220</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1907,23 +1907,23 @@
         <v>7700</v>
       </c>
       <c r="R16" t="n">
-        <v>-1097000</v>
+        <v>-1111000</v>
       </c>
       <c r="S16" t="n">
         <v>-30000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>LG디스플레이의 낮은 목표가 및 회복 불능 차트 분석. 유상증자 가능성과 회사의 장기적 전망에 대한 부정적 평가.</t>
+          <t>기업 가치 대비 낮은 목표가 제시 및 사업 불확실성에 따른 주가 하락 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['목표가', '차트', '유상증자']</t>
+          <t>['LG디스플레이', '기업가치', '플립']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>-0.6</v>
       </c>
       <c r="E17" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F17" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G17" t="n">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="H17" t="n">
         <v>3.37</v>
@@ -1990,7 +1990,7 @@
         <v>3.97</v>
       </c>
       <c r="O17" t="n">
-        <v>73040660030</v>
+        <v>73526800375</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -1999,14 +1999,14 @@
         <v>1272</v>
       </c>
       <c r="R17" t="n">
-        <v>59000</v>
+        <v>65000</v>
       </c>
       <c r="S17" t="n">
-        <v>-8000</v>
+        <v>-56000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 및 광통신 시장 성장률 분석. 유튜버 활동과 공매도 규제 언급.</t>
+          <t>3분기 실적 서프라이즈에도 불구하고 급락세 지속 및 정치 이슈 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '광통신', '공매도']</t>
+          <t>['광통신', '실적', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3940</v>
+        <v>3945</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.73%</t>
+          <t>'-7.61%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2082,7 +2082,7 @@
         <v>4.46</v>
       </c>
       <c r="O18" t="n">
-        <v>17872486082</v>
+        <v>17926249937</v>
       </c>
       <c r="P18" t="n">
         <v>5470</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25925</v>
+        <v>25900</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.74%</t>
+          <t>'-7.83%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>68</v>
       </c>
       <c r="F19" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G19" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H19" t="n">
         <v>9.460000000000001</v>
@@ -2174,7 +2174,7 @@
         <v>10.02</v>
       </c>
       <c r="O19" t="n">
-        <v>51480240250</v>
+        <v>52545203525</v>
       </c>
       <c r="P19" t="n">
         <v>75900</v>

--- a/data/trending_integrated_20261012_13.xlsx
+++ b/data/trending_integrated_20261012_13.xlsx
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19936708860</v>
+        <v>19939872540</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -670,13 +670,13 @@
         <v>0.91</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>131916950210</v>
+        <v>131999299940</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13900</v>
+        <v>13720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+24.78%</t>
+          <t>'+23.16%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F4" t="n">
         <v>78</v>
       </c>
       <c r="G4" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>166606941630</v>
+        <v>169045230730</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>금호건설, 호남 지역 건설사로서의 특성 언급. 금호전기 상장과 연동 가능성 및 외국인 대량 매도 언급.</t>
+          <t>전라도 지역 사업 언급과 함께 금호전기 상장 풀림 영향 분석. 외인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['호남', '외국인 매도', '금호전기']</t>
+          <t>['금호전기', '호남', '외인 매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1633</v>
+        <v>1619</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+17.74%</t>
+          <t>'+16.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>11028037015</v>
+        <v>11159578995</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>녹십자엠에스</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4010</v>
+        <v>7480</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.36%</t>
+          <t>'+5.65%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.19</v>
+        <v>-1.1</v>
       </c>
       <c r="E6" t="n">
+        <v>159</v>
+      </c>
+      <c r="F6" t="n">
         <v>85</v>
       </c>
-      <c r="F6" t="n">
-        <v>44</v>
-      </c>
       <c r="G6" t="n">
-        <v>101</v>
+        <v>556</v>
       </c>
       <c r="H6" t="n">
-        <v>0.78</v>
+        <v>1.99</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3735</v>
+        <v>7080</v>
       </c>
       <c r="K6" t="n">
-        <v>3660</v>
+        <v>6830</v>
       </c>
       <c r="L6" t="n">
-        <v>4300</v>
+        <v>8100</v>
       </c>
       <c r="M6" t="n">
-        <v>3660</v>
+        <v>6720</v>
       </c>
       <c r="N6" t="n">
-        <v>1.97</v>
+        <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>66026971074</v>
+        <v>108988305705</v>
       </c>
       <c r="P6" t="n">
-        <v>6660</v>
+        <v>23500</v>
       </c>
       <c r="Q6" t="n">
-        <v>2200</v>
+        <v>2890</v>
       </c>
       <c r="R6" t="n">
-        <v>60000</v>
+        <v>-79000</v>
       </c>
       <c r="S6" t="n">
-        <v>-79000</v>
+        <v>246000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>중국 방역 강화 및 러시아 관련 이슈에 따른 상승 가능성 및 매도 신호 혼재.</t>
+          <t>성수메가프로젝트 및 건설기초소재 대장주로서의 역할 언급. 공매도 쇼퀴즈 기대 및 국토부 승인 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['러시아', '방역', '수익']</t>
+          <t>['건설기초소재', '공매도', '성수메가프로젝트']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>142280</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14780</v>
+        <v>14570</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.25%</t>
+          <t>'+4.74%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>214</v>
       </c>
       <c r="F7" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G7" t="n">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="H7" t="n">
         <v>0.21</v>
@@ -1070,7 +1070,7 @@
         <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>142192376425</v>
+        <v>145736931685</v>
       </c>
       <c r="P7" t="n">
         <v>28700</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>방산 및 우주 테마와 연계된 주가 상승 기대감 속 보호예수 해제 변동성 우려.</t>
+          <t>미국 방산 대장주 팔란티어 상승과 연계하여 전쟁 긴장감 속 주가 흐름 분석. 보호예수 해제 영향 관찰.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['방산', '우주', '보호예수']</t>
+          <t>['방산', '팔란티어', '보호예수']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>녹십자엠에스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7480</v>
+        <v>3860</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.65%</t>
+          <t>'+3.35%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.1</v>
+        <v>-1.19</v>
       </c>
       <c r="E8" t="n">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="F8" t="n">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="G8" t="n">
-        <v>532</v>
+        <v>101</v>
       </c>
       <c r="H8" t="n">
-        <v>1.99</v>
+        <v>0.78</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7080</v>
+        <v>3735</v>
       </c>
       <c r="K8" t="n">
-        <v>6830</v>
+        <v>3660</v>
       </c>
       <c r="L8" t="n">
-        <v>8100</v>
+        <v>4300</v>
       </c>
       <c r="M8" t="n">
-        <v>6720</v>
+        <v>3660</v>
       </c>
       <c r="N8" t="n">
-        <v>3.09</v>
+        <v>1.97</v>
       </c>
       <c r="O8" t="n">
-        <v>106015019665</v>
+        <v>67684521109</v>
       </c>
       <c r="P8" t="n">
-        <v>23500</v>
+        <v>6660</v>
       </c>
       <c r="Q8" t="n">
-        <v>2890</v>
+        <v>2200</v>
       </c>
       <c r="R8" t="n">
+        <v>60000</v>
+      </c>
+      <c r="S8" t="n">
         <v>-79000</v>
       </c>
-      <c r="S8" t="n">
-        <v>246000</v>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>성수메가프로젝트 및 건설기초소재 대장주로서의 역할 언급. 공매도 쇼퀴즈 기대 및 국토부 승인 전망.</t>
+          <t>중국 방역 강화 소식에 따른 주가 변동 가능성 언급. 2만원 목표 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['건설기초소재', '공매도', '성수메가프로젝트']</t>
+          <t>['중국 방역', '러시아', '2만원']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>142280</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11150</v>
+        <v>45000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.68%</t>
+          <t>'-1.42%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>431</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>246</v>
       </c>
       <c r="G9" t="n">
-        <v>93</v>
+        <v>2687</v>
       </c>
       <c r="H9" t="n">
-        <v>0.41</v>
+        <v>13.33</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>11340</v>
+        <v>45650</v>
       </c>
       <c r="K9" t="n">
-        <v>11340</v>
+        <v>47550</v>
       </c>
       <c r="L9" t="n">
-        <v>12470</v>
+        <v>47550</v>
       </c>
       <c r="M9" t="n">
-        <v>10810</v>
+        <v>43900</v>
       </c>
       <c r="N9" t="n">
-        <v>0.44</v>
+        <v>13.39</v>
       </c>
       <c r="O9" t="n">
-        <v>29322630165</v>
+        <v>35158417625</v>
       </c>
       <c r="P9" t="n">
-        <v>29750</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>10810</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>8000</v>
+        <v>-112000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
+          <t>FDA 간암 1차 치료제 리보세라닙 재승인 서류 제출 공시 확인. 연말 30만 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
+          <t>['FDA', '리보세라닙', '재신청']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>486510</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44800</v>
+        <v>11080</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.86%</t>
+          <t>'-2.29%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="E10" t="n">
-        <v>424</v>
+        <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>244</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>2679</v>
+        <v>92</v>
       </c>
       <c r="H10" t="n">
-        <v>13.33</v>
+        <v>0.41</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>45650</v>
+        <v>11340</v>
       </c>
       <c r="K10" t="n">
-        <v>47550</v>
+        <v>11340</v>
       </c>
       <c r="L10" t="n">
-        <v>47550</v>
+        <v>12470</v>
       </c>
       <c r="M10" t="n">
-        <v>43900</v>
+        <v>10810</v>
       </c>
       <c r="N10" t="n">
-        <v>13.39</v>
+        <v>0.44</v>
       </c>
       <c r="O10" t="n">
-        <v>34596604175</v>
+        <v>29437957075</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>29750</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>10810</v>
       </c>
       <c r="R10" t="n">
-        <v>-112000</v>
+        <v>8000</v>
       </c>
       <c r="S10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>FDA 간암 1차 치료제 리보세라닙 재승인 서류 제출 공시 확인. 연말 30만 기대감.</t>
+          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['FDA', '리보세라닙', '재신청']</t>
+          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2235</v>
+        <v>2240</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.04%</t>
+          <t>'-2.82%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.16</v>
       </c>
       <c r="E11" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="H11" t="n">
         <v>1.48</v>
@@ -1438,7 +1438,7 @@
         <v>1.32</v>
       </c>
       <c r="O11" t="n">
-        <v>30223115632</v>
+        <v>30281969277</v>
       </c>
       <c r="P11" t="n">
         <v>2465</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16140</v>
+        <v>16150</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.18%</t>
+          <t>'-3.12%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F12" t="n">
         <v>62</v>
       </c>
       <c r="G12" t="n">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="H12" t="n">
         <v>9.470000000000001</v>
@@ -1530,7 +1530,7 @@
         <v>9.460000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>48951966830</v>
+        <v>50029882855</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>252750</v>
+        <v>1624000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.53%</t>
+          <t>'-3.39%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>482</v>
+        <v>516</v>
       </c>
       <c r="G13" t="n">
-        <v>1853</v>
+        <v>1935</v>
       </c>
       <c r="H13" t="n">
-        <v>46.35</v>
+        <v>49.52</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>262000</v>
+        <v>1681000</v>
       </c>
       <c r="K13" t="n">
-        <v>260000</v>
+        <v>1640000</v>
       </c>
       <c r="L13" t="n">
-        <v>262500</v>
+        <v>1653000</v>
       </c>
       <c r="M13" t="n">
-        <v>252000</v>
+        <v>1605000</v>
       </c>
       <c r="N13" t="n">
-        <v>46.38</v>
+        <v>49.59</v>
       </c>
       <c r="O13" t="n">
-        <v>2582027273750</v>
+        <v>3071939607500</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>90200</v>
+        <v>403000</v>
       </c>
       <c r="R13" t="n">
-        <v>-1433000</v>
+        <v>-244000</v>
       </c>
       <c r="S13" t="n">
-        <v>-345000</v>
+        <v>13000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈로 인한 급락 및 외인/기관 매도 우려 언급.</t>
+          <t>정치적 이슈와 연계된 한국 증시 전반의 하락세에 대한 강한 불만 표출.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치', '반도체', '외인']</t>
+          <t>['정치', '하락세', 'SK하이닉스']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1619000</v>
+        <v>253000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.69%</t>
+          <t>'-3.44%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E14" t="n">
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="G14" t="n">
-        <v>1967</v>
+        <v>1843</v>
       </c>
       <c r="H14" t="n">
-        <v>49.52</v>
+        <v>46.35</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1681000</v>
+        <v>262000</v>
       </c>
       <c r="K14" t="n">
-        <v>1640000</v>
+        <v>260000</v>
       </c>
       <c r="L14" t="n">
-        <v>1653000</v>
+        <v>262500</v>
       </c>
       <c r="M14" t="n">
-        <v>1605000</v>
+        <v>252000</v>
       </c>
       <c r="N14" t="n">
-        <v>49.59</v>
+        <v>46.38</v>
       </c>
       <c r="O14" t="n">
-        <v>2984378343000</v>
+        <v>2650206289500</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R14" t="n">
-        <v>-244000</v>
+        <v>-1433000</v>
       </c>
       <c r="S14" t="n">
-        <v>13000</v>
+        <v>-345000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 요인으로 인한 증시 하락 및 반도체 업황 부진에 따른 주가 하락 우려.</t>
+          <t>정치적 이슈와 연계된 한국 증시 전반의 하락세에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '반도체', '정치']</t>
+          <t>['정치', '하락세', '대국민 사기극']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18160</v>
+        <v>18170</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.71%</t>
+          <t>'-3.66%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F15" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G15" t="n">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="H15" t="n">
         <v>27.61</v>
@@ -1806,7 +1806,7 @@
         <v>27.68</v>
       </c>
       <c r="O15" t="n">
-        <v>36826209765</v>
+        <v>38347082050</v>
       </c>
       <c r="P15" t="n">
         <v>35350</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7750</v>
+        <v>7800</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.02%</t>
+          <t>'-4.41%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F16" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G16" t="n">
-        <v>737</v>
+        <v>750</v>
       </c>
       <c r="H16" t="n">
         <v>26.37</v>
@@ -1898,7 +1898,7 @@
         <v>26.38</v>
       </c>
       <c r="O16" t="n">
-        <v>23386454220</v>
+        <v>24077785760</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>기업 가치 대비 낮은 목표가 제시 및 사업 불확실성에 따른 주가 하락 전망.</t>
+          <t>삼성디스플레이와의 기업 가치 비교 및 유상증자 가능성 언급. 차트 회복 불능 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['LG디스플레이', '기업가치', '플립']</t>
+          <t>['삼성디스플레이', '유상증자', '차트']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15850</v>
+        <v>15950</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.60%</t>
+          <t>'-6.01%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>139</v>
       </c>
       <c r="F17" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G17" t="n">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="H17" t="n">
         <v>3.37</v>
@@ -1990,7 +1990,7 @@
         <v>3.97</v>
       </c>
       <c r="O17" t="n">
-        <v>73526800375</v>
+        <v>74069368065</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3945</v>
+        <v>26000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.61%</t>
+          <t>'-7.47%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-2.94</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F18" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="G18" t="n">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="H18" t="n">
-        <v>1.52</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>4270</v>
+        <v>28100</v>
       </c>
       <c r="K18" t="n">
-        <v>4150</v>
+        <v>27600</v>
       </c>
       <c r="L18" t="n">
-        <v>4495</v>
+        <v>27800</v>
       </c>
       <c r="M18" t="n">
-        <v>3905</v>
+        <v>25850</v>
       </c>
       <c r="N18" t="n">
-        <v>4.46</v>
+        <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>17926249937</v>
+        <v>53233094925</v>
       </c>
       <c r="P18" t="n">
-        <v>5470</v>
+        <v>75900</v>
       </c>
       <c r="Q18" t="n">
-        <v>2810</v>
+        <v>15960</v>
       </c>
       <c r="R18" t="n">
-        <v>-89000</v>
+        <v>-64000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>러시아 코로나 관련 뉴스 언급, 모더나 급등 영향 분석. 명확한 모멘텀 부재 속 단기적 기대감.</t>
+          <t>경영진의 무능력 지적, LS 기술유출 타격 언급. 실적 개선 근거 부족 및 투매 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['코로나19', '모더나', '단기 모멘텀']</t>
+          <t>['경영진 부진', '기술유출', '실적 우려']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25900</v>
+        <v>3910</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.83%</t>
+          <t>'-8.43%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-2.94</v>
       </c>
       <c r="E19" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="F19" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="G19" t="n">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="H19" t="n">
-        <v>9.460000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>28100</v>
+        <v>4270</v>
       </c>
       <c r="K19" t="n">
-        <v>27600</v>
+        <v>4150</v>
       </c>
       <c r="L19" t="n">
-        <v>27800</v>
+        <v>4495</v>
       </c>
       <c r="M19" t="n">
-        <v>25850</v>
+        <v>3905</v>
       </c>
       <c r="N19" t="n">
-        <v>10.02</v>
+        <v>4.46</v>
       </c>
       <c r="O19" t="n">
-        <v>52545203525</v>
+        <v>17995866307</v>
       </c>
       <c r="P19" t="n">
-        <v>75900</v>
+        <v>5470</v>
       </c>
       <c r="Q19" t="n">
-        <v>15960</v>
+        <v>2810</v>
       </c>
       <c r="R19" t="n">
-        <v>-64000</v>
+        <v>-89000</v>
       </c>
       <c r="S19" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>경영진의 무능력 지적, LS 기술유출 타격 언급. 실적 개선 근거 부족 및 투매 우려.</t>
+          <t>러시아 코로나 관련 뉴스 언급, 모더나 급등 영향 분석. 명확한 모멘텀 부재 속 단기적 기대감.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['경영진 부진', '기술유출', '실적 우려']</t>
+          <t>['코로나19', '모더나', '단기 모멘텀']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>002720</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261012_13.xlsx
+++ b/data/trending_integrated_20261012_13.xlsx
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19939872540</v>
+        <v>19948843060</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -673,10 +673,10 @@
         <v>52</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>131999299940</v>
+        <v>132023432540</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13720</v>
+        <v>13640</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+23.16%</t>
+          <t>'+22.44%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F4" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G4" t="n">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>169045230730</v>
+        <v>170812281815</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>전라도 지역 사업 언급과 함께 금호전기 상장 풀림 영향 분석. 외인 매도세 관찰.</t>
+          <t>외인 대량 매도 속에서 금호전기 상장 및 금호건설 호남 테마 언급. 상승 여력에 대한 불확실성 존재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['금호전기', '호남', '외인 매도']</t>
+          <t>['호남 테마', '외인 매도', '금호전기']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1619</v>
+        <v>1599</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+16.73%</t>
+          <t>'+15.28%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
         <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>11159578995</v>
+        <v>11230919776</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7480</v>
+        <v>7630</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.65%</t>
+          <t>'+7.77%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F6" t="n">
         <v>85</v>
       </c>
       <c r="G6" t="n">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="H6" t="n">
         <v>1.99</v>
@@ -978,7 +978,7 @@
         <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>108988305705</v>
+        <v>112350925225</v>
       </c>
       <c r="P6" t="n">
         <v>23500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>성수메가프로젝트 및 건설기초소재 대장주로서의 역할 언급. 공매도 쇼퀴즈 기대 및 국토부 승인 전망.</t>
+          <t>성수 메가프로젝트 및 건설 기초 소재 대장주로서의 잠재력 언급. 공매도 세력과의 대립 및 재개발 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['건설기초소재', '공매도', '성수메가프로젝트']</t>
+          <t>['성수 메가프로젝트', '건설 기초소재', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14570</v>
+        <v>14600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.74%</t>
+          <t>'+4.96%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F7" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G7" t="n">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="H7" t="n">
         <v>0.21</v>
@@ -1070,7 +1070,7 @@
         <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>145736931685</v>
+        <v>147300661795</v>
       </c>
       <c r="P7" t="n">
         <v>28700</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 방산 대장주 팔란티어 상승과 연계하여 전쟁 긴장감 속 주가 흐름 분석. 보호예수 해제 영향 관찰.</t>
+          <t>상승 여부에 대한 불확실성과 개인 투자자 꼬임에 대한 우려. 방산 테마 언급 및 주가 변동성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['방산', '팔란티어', '보호예수']</t>
+          <t>['상승 불확실', '개미 꼬임', '방산 테마']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3860</v>
+        <v>3830</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.35%</t>
+          <t>'+2.54%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-1.19</v>
       </c>
       <c r="E8" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H8" t="n">
         <v>0.78</v>
@@ -1162,7 +1162,7 @@
         <v>1.97</v>
       </c>
       <c r="O8" t="n">
-        <v>67684521109</v>
+        <v>68970060876</v>
       </c>
       <c r="P8" t="n">
         <v>6660</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>중국 방역 강화 소식에 따른 주가 변동 가능성 언급. 2만원 목표 기대.</t>
+          <t>러시아 발 방역 강화 조치에 따른 상승 기대감과 매도 의견 혼재. 특정 가격대 돌파 시 추가 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['중국 방역', '러시아', '2만원']</t>
+          <t>['러시아 방역', '수익 실현', '추가 상승']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45000</v>
+        <v>11190</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.42%</t>
+          <t>'-1.32%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="E9" t="n">
-        <v>431</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>246</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>2687</v>
+        <v>94</v>
       </c>
       <c r="H9" t="n">
-        <v>13.33</v>
+        <v>0.41</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>45650</v>
+        <v>11340</v>
       </c>
       <c r="K9" t="n">
-        <v>47550</v>
+        <v>11340</v>
       </c>
       <c r="L9" t="n">
-        <v>47550</v>
+        <v>12470</v>
       </c>
       <c r="M9" t="n">
-        <v>43900</v>
+        <v>10810</v>
       </c>
       <c r="N9" t="n">
-        <v>13.39</v>
+        <v>0.44</v>
       </c>
       <c r="O9" t="n">
-        <v>35158417625</v>
+        <v>29593845155</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>29750</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>10810</v>
       </c>
       <c r="R9" t="n">
-        <v>-112000</v>
+        <v>8000</v>
       </c>
       <c r="S9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>FDA 간암 1차 치료제 리보세라닙 재승인 서류 제출 공시 확인. 연말 30만 기대감.</t>
+          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA', '리보세라닙', '재신청']</t>
+          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11080</v>
+        <v>44750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.29%</t>
+          <t>'-1.97%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>442</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>249</v>
       </c>
       <c r="G10" t="n">
-        <v>92</v>
+        <v>2691</v>
       </c>
       <c r="H10" t="n">
-        <v>0.41</v>
+        <v>13.33</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>11340</v>
+        <v>45650</v>
       </c>
       <c r="K10" t="n">
-        <v>11340</v>
+        <v>47550</v>
       </c>
       <c r="L10" t="n">
-        <v>12470</v>
+        <v>47550</v>
       </c>
       <c r="M10" t="n">
-        <v>10810</v>
+        <v>43900</v>
       </c>
       <c r="N10" t="n">
-        <v>0.44</v>
+        <v>13.39</v>
       </c>
       <c r="O10" t="n">
-        <v>29437957075</v>
+        <v>35556807050</v>
       </c>
       <c r="P10" t="n">
-        <v>29750</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>10810</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>8000</v>
+        <v>-112000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
+          <t>FDA 간암 1차 치료제 리보세라닙 재승인 서류 제출 공시 확인. 연말 30만 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
+          <t>['FDA', '리보세라닙', '재신청']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>486510</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2240</v>
+        <v>2245</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.82%</t>
+          <t>'-2.60%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.16</v>
       </c>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H11" t="n">
         <v>1.48</v>
@@ -1438,7 +1438,7 @@
         <v>1.32</v>
       </c>
       <c r="O11" t="n">
-        <v>30281969277</v>
+        <v>30454888386</v>
       </c>
       <c r="P11" t="n">
         <v>2465</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 확대 따른 에너지저장장치용 유연회로기판 매출 급증 기대. 단기 급등 후 차익실현 압력.</t>
+          <t>대표이사 및 회사 운영에 대한 비판과 함께 주가 상승에 대한 기대감 표출. IR 인터뷰 게재 사실 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', 'ESS', '유연회로기판']</t>
+          <t>['대표이사 비판', '주가 상승 기대', 'IR 인터뷰']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16150</v>
+        <v>16210</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.12%</t>
+          <t>'-2.76%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="F12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G12" t="n">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="H12" t="n">
         <v>9.470000000000001</v>
@@ -1530,7 +1530,7 @@
         <v>9.460000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>50029882855</v>
+        <v>51377700775</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대규모 대차 거래 해지 및 뱅크런 가능성 제기로 인한 주가 하락 우려.</t>
+          <t>대차 해지와 관련한 의혹 제기 및 뱅크런 언급. 주가 하락에 대한 불만과 범죄 행위 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['대차거래', '뱅크런', '주주연대']</t>
+          <t>['대차 해지', '뱅크런', '주가 하락']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1624000</v>
+        <v>1633000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.39%</t>
+          <t>'-2.86%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>516</v>
       </c>
       <c r="G13" t="n">
-        <v>1935</v>
+        <v>1967</v>
       </c>
       <c r="H13" t="n">
         <v>49.52</v>
@@ -1622,7 +1622,7 @@
         <v>49.59</v>
       </c>
       <c r="O13" t="n">
-        <v>3071939607500</v>
+        <v>3156110089000</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 한국 증시 전반의 하락세에 대한 강한 불만 표출.</t>
+          <t>정치적 요인으로 인한 주가 하락에 대한 불만 표출. 반도체 업황 및 증권사 목표가 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치', '하락세', 'SK하이닉스']</t>
+          <t>['정치적 요인', '주가 하락', '반도체 업황']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G14" t="n">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="H14" t="n">
         <v>46.35</v>
@@ -1714,7 +1714,7 @@
         <v>46.38</v>
       </c>
       <c r="O14" t="n">
-        <v>2650206289500</v>
+        <v>2736695959250</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 한국 증시 전반의 하락세에 대한 부정적 전망.</t>
+          <t>정치적 이슈와 맞물린 하락세에 대한 불만 표출. 반도체 관련 내용이나 구체적 분석 부재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['정치', '하락세', '대국민 사기극']</t>
+          <t>['정치적 이슈', '하락세', '개미 빚투']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18170</v>
+        <v>18200</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.66%</t>
+          <t>'-3.50%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F15" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G15" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H15" t="n">
         <v>27.61</v>
@@ -1806,7 +1806,7 @@
         <v>27.68</v>
       </c>
       <c r="O15" t="n">
-        <v>38347082050</v>
+        <v>40919340230</v>
       </c>
       <c r="P15" t="n">
         <v>35350</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7800</v>
+        <v>7795</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.41%</t>
+          <t>'-4.47%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F16" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G16" t="n">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="H16" t="n">
         <v>26.37</v>
@@ -1898,7 +1898,7 @@
         <v>26.38</v>
       </c>
       <c r="O16" t="n">
-        <v>24077785760</v>
+        <v>24589855840</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>삼성디스플레이와의 기업 가치 비교 및 유상증자 가능성 언급. 차트 회복 불능 전망.</t>
+          <t>기업의 존폐 및 유상증자 가능성에 대한 부정적 전망. 삼성디스플레이와의 비교 및 실적 부진 우려.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['삼성디스플레이', '유상증자', '차트']</t>
+          <t>['유상증자', '존폐 우려', '실적 부진']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15950</v>
+        <v>15970</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.01%</t>
+          <t>'-5.89%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.6</v>
       </c>
       <c r="E17" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F17" t="n">
         <v>74</v>
       </c>
       <c r="G17" t="n">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="H17" t="n">
         <v>3.37</v>
@@ -1990,7 +1990,7 @@
         <v>3.97</v>
       </c>
       <c r="O17" t="n">
-        <v>74069368065</v>
+        <v>75101058545</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2050,13 +2050,13 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F18" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G18" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H18" t="n">
         <v>9.460000000000001</v>
@@ -2082,7 +2082,7 @@
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>53233094925</v>
+        <v>54775632450</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3910</v>
+        <v>3900</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-8.43%</t>
+          <t>'-8.67%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2168,13 +2168,13 @@
         <v>4495</v>
       </c>
       <c r="M19" t="n">
-        <v>3905</v>
+        <v>3895</v>
       </c>
       <c r="N19" t="n">
         <v>4.46</v>
       </c>
       <c r="O19" t="n">
-        <v>17995866307</v>
+        <v>18109043247</v>
       </c>
       <c r="P19" t="n">
         <v>5470</v>

--- a/data/trending_integrated_20261012_13.xlsx
+++ b/data/trending_integrated_20261012_13.xlsx
@@ -578,13 +578,13 @@
         <v>0.61</v>
       </c>
       <c r="E2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19948843060</v>
+        <v>19950316740</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -676,7 +676,7 @@
         <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>132023432540</v>
+        <v>132036428720</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13640</v>
+        <v>13770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+22.44%</t>
+          <t>'+23.61%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F4" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G4" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>170812281815</v>
+        <v>172602739710</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외인 대량 매도 속에서 금호전기 상장 및 금호건설 호남 테마 언급. 상승 여력에 대한 불확실성 존재.</t>
+          <t>외인 대량 매도 확인, 금호전기 상장 영향 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['호남 테마', '외인 매도', '금호전기']</t>
+          <t>['외인 매도', '금호전기']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.28%</t>
+          <t>'+15.07%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>11230919776</v>
+        <v>11269858207</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7630</v>
+        <v>7710</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.77%</t>
+          <t>'+8.90%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F6" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G6" t="n">
-        <v>567</v>
+        <v>584</v>
       </c>
       <c r="H6" t="n">
         <v>1.99</v>
@@ -978,7 +978,7 @@
         <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>112350925225</v>
+        <v>114338836800</v>
       </c>
       <c r="P6" t="n">
         <v>23500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>성수 메가프로젝트 및 건설 기초 소재 대장주로서의 잠재력 언급. 공매도 세력과의 대립 및 재개발 기대감.</t>
+          <t>건설 기초 소재 관련 긍정적 전망, 공매도 세력과의 싸움 예상.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['성수 메가프로젝트', '건설 기초소재', '공매도']</t>
+          <t>['건설 기초 소재', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14600</v>
+        <v>14450</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.96%</t>
+          <t>'+3.88%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="F7" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G7" t="n">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="H7" t="n">
         <v>0.21</v>
@@ -1070,7 +1070,7 @@
         <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>147300661795</v>
+        <v>148984637405</v>
       </c>
       <c r="P7" t="n">
         <v>28700</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3830</v>
+        <v>3815</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.54%</t>
+          <t>'+2.14%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-1.19</v>
       </c>
       <c r="E8" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F8" t="n">
         <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H8" t="n">
         <v>0.78</v>
@@ -1162,7 +1162,7 @@
         <v>1.97</v>
       </c>
       <c r="O8" t="n">
-        <v>68970060876</v>
+        <v>69774983890</v>
       </c>
       <c r="P8" t="n">
         <v>6660</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>러시아 발 방역 강화 조치에 따른 상승 기대감과 매도 의견 혼재. 특정 가격대 돌파 시 추가 상승 가능성 언급.</t>
+          <t>러시아 방역 강화 관련 소식 언급, 단기 급등 후 차익 실현 가능성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['러시아 방역', '수익 실현', '추가 상승']</t>
+          <t>['러시아 방역', '차익 실현']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11190</v>
+        <v>44900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.32%</t>
+          <t>'-1.64%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>449</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>249</v>
       </c>
       <c r="G9" t="n">
-        <v>94</v>
+        <v>2724</v>
       </c>
       <c r="H9" t="n">
-        <v>0.41</v>
+        <v>13.33</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>11340</v>
+        <v>45650</v>
       </c>
       <c r="K9" t="n">
-        <v>11340</v>
+        <v>47550</v>
       </c>
       <c r="L9" t="n">
-        <v>12470</v>
+        <v>47550</v>
       </c>
       <c r="M9" t="n">
-        <v>10810</v>
+        <v>43900</v>
       </c>
       <c r="N9" t="n">
-        <v>0.44</v>
+        <v>13.39</v>
       </c>
       <c r="O9" t="n">
-        <v>29593845155</v>
+        <v>35766755975</v>
       </c>
       <c r="P9" t="n">
-        <v>29750</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>10810</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>8000</v>
+        <v>-112000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
+          <t>FDA 간암 1차 치료제 리보세라닙 재승인 서류 제출 공시 확인. 연말 30만 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
+          <t>['FDA', '리보세라닙', '재신청']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>486510</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44750</v>
+        <v>2250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.97%</t>
+          <t>'-2.39%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.06</v>
+        <v>0.16</v>
       </c>
       <c r="E10" t="n">
-        <v>442</v>
+        <v>82</v>
       </c>
       <c r="F10" t="n">
-        <v>249</v>
+        <v>39</v>
       </c>
       <c r="G10" t="n">
-        <v>2691</v>
+        <v>137</v>
       </c>
       <c r="H10" t="n">
-        <v>13.33</v>
+        <v>1.48</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>45650</v>
+        <v>2305</v>
       </c>
       <c r="K10" t="n">
-        <v>47550</v>
+        <v>2430</v>
       </c>
       <c r="L10" t="n">
-        <v>47550</v>
+        <v>2445</v>
       </c>
       <c r="M10" t="n">
-        <v>43900</v>
+        <v>2210</v>
       </c>
       <c r="N10" t="n">
-        <v>13.39</v>
+        <v>1.32</v>
       </c>
       <c r="O10" t="n">
-        <v>35556807050</v>
+        <v>30633056966</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>2465</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>865</v>
       </c>
       <c r="R10" t="n">
-        <v>-112000</v>
+        <v>-498000</v>
       </c>
       <c r="S10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>FDA 간암 1차 치료제 리보세라닙 재승인 서류 제출 공시 확인. 연말 30만 기대감.</t>
+          <t>대표이사 및 회사 운영에 대한 비판과 함께 주가 상승에 대한 기대감 표출. IR 인터뷰 게재 사실 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['FDA', '리보세라닙', '재신청']</t>
+          <t>['대표이사 비판', '주가 상승 기대', 'IR 인터뷰']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2245</v>
+        <v>16230</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.60%</t>
+          <t>'-2.64%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.16</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="G11" t="n">
-        <v>137</v>
+        <v>724</v>
       </c>
       <c r="H11" t="n">
-        <v>1.48</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2305</v>
+        <v>16670</v>
       </c>
       <c r="K11" t="n">
-        <v>2430</v>
+        <v>16500</v>
       </c>
       <c r="L11" t="n">
-        <v>2445</v>
+        <v>16870</v>
       </c>
       <c r="M11" t="n">
-        <v>2210</v>
+        <v>16050</v>
       </c>
       <c r="N11" t="n">
-        <v>1.32</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>30454888386</v>
+        <v>52263030200</v>
       </c>
       <c r="P11" t="n">
-        <v>2465</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>865</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-498000</v>
+        <v>544000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-97000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대표이사 및 회사 운영에 대한 비판과 함께 주가 상승에 대한 기대감 표출. IR 인터뷰 게재 사실 언급.</t>
+          <t>대차 해지와 관련한 의혹 제기 및 뱅크런 언급. 주가 하락에 대한 불만과 범죄 행위 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['대표이사 비판', '주가 상승 기대', 'IR 인터뷰']</t>
+          <t>['대차 해지', '뱅크런', '주가 하락']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,99 +1476,99 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16210</v>
+        <v>11020</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.76%</t>
+          <t>'-2.82%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="E12" t="n">
-        <v>166</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="G12" t="n">
-        <v>712</v>
+        <v>94</v>
       </c>
       <c r="H12" t="n">
-        <v>9.470000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16670</v>
+        <v>11340</v>
       </c>
       <c r="K12" t="n">
-        <v>16500</v>
+        <v>11340</v>
       </c>
       <c r="L12" t="n">
-        <v>16870</v>
+        <v>12470</v>
       </c>
       <c r="M12" t="n">
-        <v>16050</v>
+        <v>10810</v>
       </c>
       <c r="N12" t="n">
-        <v>9.460000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="O12" t="n">
-        <v>51377700775</v>
+        <v>29666846035</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>29750</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>10810</v>
       </c>
       <c r="R12" t="n">
-        <v>544000</v>
+        <v>8000</v>
       </c>
       <c r="S12" t="n">
-        <v>-97000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대차 해지와 관련한 의혹 제기 및 뱅크런 언급. 주가 하락에 대한 불만과 범죄 행위 언급.</t>
+          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['대차 해지', '뱅크런', '주가 하락']</t>
+          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1633000</v>
+        <v>1630000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.86%</t>
+          <t>'-3.03%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G13" t="n">
-        <v>1967</v>
+        <v>1941</v>
       </c>
       <c r="H13" t="n">
         <v>49.52</v>
@@ -1622,7 +1622,7 @@
         <v>49.59</v>
       </c>
       <c r="O13" t="n">
-        <v>3156110089000</v>
+        <v>3257206301500</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 요인으로 인한 주가 하락에 대한 불만 표출. 반도체 업황 및 증권사 목표가 언급.</t>
+          <t>정치적 요인으로 인한 주가 폭락 분석, 증권사 목표가 하향 조정 가능성.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치적 요인', '주가 하락', '반도체 업황']</t>
+          <t>['정치적 요인', '목표가 하향']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>253000</v>
+        <v>18190</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.44%</t>
+          <t>'-3.55%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>119</v>
       </c>
       <c r="F14" t="n">
-        <v>491</v>
+        <v>68</v>
       </c>
       <c r="G14" t="n">
-        <v>1844</v>
+        <v>338</v>
       </c>
       <c r="H14" t="n">
-        <v>46.35</v>
+        <v>27.61</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>262000</v>
+        <v>18860</v>
       </c>
       <c r="K14" t="n">
-        <v>260000</v>
+        <v>18690</v>
       </c>
       <c r="L14" t="n">
-        <v>262500</v>
+        <v>18760</v>
       </c>
       <c r="M14" t="n">
-        <v>252000</v>
+        <v>18100</v>
       </c>
       <c r="N14" t="n">
-        <v>46.38</v>
+        <v>27.68</v>
       </c>
       <c r="O14" t="n">
-        <v>2736695959250</v>
+        <v>41656464815</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>90200</v>
+        <v>18100</v>
       </c>
       <c r="R14" t="n">
-        <v>-1433000</v>
+        <v>112000</v>
       </c>
       <c r="S14" t="n">
-        <v>-345000</v>
+        <v>33000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈와 맞물린 하락세에 대한 불만 표출. 반도체 관련 내용이나 구체적 분석 부재.</t>
+          <t>LNG·FLNG 수주 랠리에도 불구하고 하락세 지속, 정치적 요인 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '하락세', '개미 빚투']</t>
+          <t>['수주 랠리', '정치적 요인']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18200</v>
+        <v>252500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.50%</t>
+          <t>'-3.63%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E15" t="n">
-        <v>118</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>67</v>
+        <v>497</v>
       </c>
       <c r="G15" t="n">
-        <v>336</v>
+        <v>1869</v>
       </c>
       <c r="H15" t="n">
-        <v>27.61</v>
+        <v>46.35</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18860</v>
+        <v>262000</v>
       </c>
       <c r="K15" t="n">
-        <v>18690</v>
+        <v>260000</v>
       </c>
       <c r="L15" t="n">
-        <v>18760</v>
+        <v>262500</v>
       </c>
       <c r="M15" t="n">
-        <v>18100</v>
+        <v>252000</v>
       </c>
       <c r="N15" t="n">
-        <v>27.68</v>
+        <v>46.38</v>
       </c>
       <c r="O15" t="n">
-        <v>40919340230</v>
+        <v>2845535706750</v>
       </c>
       <c r="P15" t="n">
-        <v>35350</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>18100</v>
+        <v>90200</v>
       </c>
       <c r="R15" t="n">
-        <v>112000</v>
+        <v>-1433000</v>
       </c>
       <c r="S15" t="n">
-        <v>33000</v>
+        <v>-345000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>조선주 순환매 및 LNG·FLNG 수주 랠리 언급. 현대로템, 한화오션과의 비교 및 국내 증시 하락세 분석.</t>
+          <t>정치적 요인으로 인한 하락 원인 분석, 외인/기관 매도세 집중.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['조선주', '수주', 'LNG']</t>
+          <t>['정치적 요인', '외인 매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7795</v>
+        <v>7810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.47%</t>
+          <t>'-4.29%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F16" t="n">
         <v>90</v>
       </c>
       <c r="G16" t="n">
-        <v>765</v>
+        <v>791</v>
       </c>
       <c r="H16" t="n">
         <v>26.37</v>
@@ -1898,7 +1898,7 @@
         <v>26.38</v>
       </c>
       <c r="O16" t="n">
-        <v>24589855840</v>
+        <v>25135059985</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>기업의 존폐 및 유상증자 가능성에 대한 부정적 전망. 삼성디스플레이와의 비교 및 실적 부진 우려.</t>
+          <t>기업 가치 저평가 및 재무 악화 우려, 유상증자 가능성 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['유상증자', '존폐 우려', '실적 부진']</t>
+          <t>['기업 가치', '유상증자']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15970</v>
+        <v>15940</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.89%</t>
+          <t>'-6.07%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>74</v>
       </c>
       <c r="G17" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="H17" t="n">
         <v>3.37</v>
@@ -1990,7 +1990,7 @@
         <v>3.97</v>
       </c>
       <c r="O17" t="n">
-        <v>75101058545</v>
+        <v>75631545065</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2050,13 +2050,13 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F18" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H18" t="n">
         <v>9.460000000000001</v>
@@ -2082,7 +2082,7 @@
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>54775632450</v>
+        <v>55762866125</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3900</v>
+        <v>3860</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-8.67%</t>
+          <t>'-9.60%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-2.94</v>
       </c>
       <c r="E19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G19" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="H19" t="n">
         <v>1.52</v>
@@ -2168,13 +2168,13 @@
         <v>4495</v>
       </c>
       <c r="M19" t="n">
-        <v>3895</v>
+        <v>3840</v>
       </c>
       <c r="N19" t="n">
         <v>4.46</v>
       </c>
       <c r="O19" t="n">
-        <v>18109043247</v>
+        <v>18355483609</v>
       </c>
       <c r="P19" t="n">
         <v>5470</v>
